--- a/event_registration_forms/026_product_line_reveal_rsvp_form--event_registration_forms.xlsx
+++ b/event_registration_forms/026_product_line_reveal_rsvp_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>event_details</t>
+          <t>event_details_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Event Details</t>
+          <t>Event Details 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rsvp</t>
+          <t>rsvp_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RSVP</t>
+          <t>Rsvp 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1160,7 +1160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rsvp_choices</t>
+          <t>rsvp_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rsvp_choices</t>
+          <t>rsvp_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
